--- a/output/DTR_7-4_PASTRANA_A.xlsx
+++ b/output/DTR_7-4_PASTRANA_A.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -74,6 +74,18 @@
   </si>
   <si>
     <t>Minutes</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Eid'l Fitr</t>
+  </si>
+  <si>
+    <t>Sunday / Palm Sunday</t>
   </si>
   <si>
     <t>Total</t>
@@ -843,14 +855,16 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="H19" s="23"/>
+      <c r="H19" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20" spans="1:11" s="7" customFormat="1">
       <c r="A20" s="22">
         <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -905,7 +919,9 @@
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="H25" s="23"/>
+      <c r="H25" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="26" spans="1:11" s="7" customFormat="1">
       <c r="A26" s="21">
@@ -915,7 +931,9 @@
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="H26" s="23"/>
+      <c r="H26" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="27" spans="1:11" s="7" customFormat="1">
       <c r="A27" s="22">
@@ -932,7 +950,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -977,7 +995,9 @@
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
-      <c r="H32" s="23"/>
+      <c r="H32" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="33" spans="1:11" s="7" customFormat="1">
       <c r="A33" s="21">
@@ -987,7 +1007,9 @@
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
-      <c r="H33" s="23"/>
+      <c r="H33" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="34" spans="1:11" s="7" customFormat="1">
       <c r="A34" s="22">
@@ -1037,7 +1059,9 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="H38" s="23"/>
+      <c r="H38" s="23" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="39" spans="1:11" s="8" customFormat="1">
       <c r="A39" s="21">
@@ -1047,7 +1071,9 @@
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
-      <c r="H39" s="23"/>
+      <c r="H39" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="40" spans="1:11" s="7" customFormat="1">
       <c r="A40" s="21">
@@ -1057,14 +1083,16 @@
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
-      <c r="H40" s="23"/>
+      <c r="H40" s="23" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="41" spans="1:11" s="7" customFormat="1">
       <c r="A41" s="22">
         <v>23</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
@@ -1076,7 +1104,7 @@
         <v>24</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -1121,7 +1149,9 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="H46" s="23"/>
+      <c r="H46" s="23" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="47" spans="1:11" s="7" customFormat="1">
       <c r="A47" s="21">
@@ -1131,14 +1161,16 @@
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
-      <c r="H47" s="23"/>
+      <c r="H47" s="23" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="48" spans="1:11" s="7" customFormat="1">
       <c r="A48" s="24">
         <v>30</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
@@ -1157,7 +1189,7 @@
     </row>
     <row r="50" spans="1:11" s="7" customFormat="1">
       <c r="A50" s="25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G50" s="26" t="str">
         <f>SUM(G20:G49)</f>
@@ -1168,12 +1200,12 @@
     <row r="51" spans="1:11" s="7" customFormat="1"/>
     <row r="52" spans="1:11" s="7" customFormat="1">
       <c r="A52" s="27" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:11" s="7" customFormat="1">
       <c r="A53" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
@@ -1184,29 +1216,29 @@
     </row>
     <row r="56" spans="1:11" s="7" customFormat="1">
       <c r="A56" s="29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:11" s="7" customFormat="1"/>
     <row r="58" spans="1:11" s="7" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:11" s="7" customFormat="1">
       <c r="B59" s="31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:11" s="7" customFormat="1"/>
     <row r="61" spans="1:11" s="7" customFormat="1">
       <c r="A61" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="7" customFormat="1">
       <c r="A62" s="16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63" spans="1:11" customHeight="1" ht="15" s="7" customFormat="1"/>
@@ -1297,47 +1329,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/output/DTR_7-4_PASTRANA_A.xlsx
+++ b/output/DTR_7-4_PASTRANA_A.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -115,13 +115,31 @@
     <t>08:02</t>
   </si>
   <si>
+    <t>15:04</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
     <t>07:25</t>
   </si>
   <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>15:39</t>
+  </si>
+  <si>
     <t>07:50</t>
   </si>
   <si>
+    <t>15:11</t>
+  </si>
+  <si>
     <t>07:31</t>
+  </si>
+  <si>
+    <t>15:00</t>
   </si>
   <si>
     <t>07:30</t>
@@ -868,7 +886,9 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="E20" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:11" s="7" customFormat="1">
@@ -878,7 +898,9 @@
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>32</v>
+      </c>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:11" s="8" customFormat="1">
@@ -950,11 +972,13 @@
         <v>10</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="E28" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="H28" s="7"/>
     </row>
     <row r="29" spans="1:11" s="7" customFormat="1">
@@ -974,7 +998,9 @@
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="H30" s="7"/>
     </row>
     <row r="31" spans="1:11" s="7" customFormat="1">
@@ -1092,11 +1118,13 @@
         <v>23</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="E41" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="H41" s="7"/>
     </row>
     <row r="42" spans="1:11" s="8" customFormat="1">
@@ -1104,11 +1132,13 @@
         <v>24</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>39</v>
+      </c>
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:11" s="8" customFormat="1">
@@ -1170,11 +1200,13 @@
         <v>30</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7" t="s">
+        <v>31</v>
+      </c>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="1:11" s="7" customFormat="1">
@@ -1329,47 +1361,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
